--- a/code-wb/code/results/结果提交.xlsx
+++ b/code-wb/code/results/结果提交.xlsx
@@ -22,13 +22,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +50,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,47 +434,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>架次编号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>服务区编号</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>机型编号</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>货箱编号列表</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>总质量（kg）</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>总体积（m³）</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>往返时间（s）</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>架次能耗（kWh）</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>返航SOC（%）</t>
         </is>
@@ -1149,42 +1161,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>架次编号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>无人机编号</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>机型编号</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>电池编号</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>开始时刻（s）</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>访问服务区顺序</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>返回O01时刻（s）</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>架次能耗（kWh）</t>
         </is>
@@ -1817,22 +1829,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>货箱编号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>架次编号</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>服务区编号</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>交付完成时刻（s）</t>
         </is>
@@ -3449,61 +3461,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>中继架次编号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>中继无人机编号</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>能源组件编号</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>开始时刻（s）</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>悬停经度（°）</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>悬停纬度（°）</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>悬停海拔（m）</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>建链完成时刻（s）</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>服务结束时刻（s）</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>返回O01时刻（s）</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>架次能耗（kWh）</t>
         </is>
@@ -3526,28 +3538,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>144.2</v>
+        <v>71.3</v>
       </c>
       <c r="E2" t="n">
-        <v>109.2050086</v>
+        <v>109.2753561</v>
       </c>
       <c r="F2" t="n">
-        <v>23.0456792</v>
+        <v>23.0240955</v>
       </c>
       <c r="G2" t="n">
-        <v>706.7</v>
+        <v>707.1</v>
       </c>
       <c r="H2" t="n">
-        <v>779.4</v>
+        <v>751</v>
       </c>
       <c r="I2" t="n">
-        <v>7137</v>
+        <v>4515.4</v>
       </c>
       <c r="J2" t="n">
-        <v>7562.2</v>
+        <v>4985.2</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2305</v>
+        <v>1.4697</v>
       </c>
     </row>
     <row r="3">
@@ -3567,28 +3579,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>216</v>
+        <v>333</v>
       </c>
       <c r="E3" t="n">
-        <v>109.2675397</v>
+        <v>109.2089168</v>
       </c>
       <c r="F3" t="n">
-        <v>23.0133036</v>
+        <v>23.0204982</v>
       </c>
       <c r="G3" t="n">
-        <v>669.6</v>
+        <v>346.5</v>
       </c>
       <c r="H3" t="n">
-        <v>757</v>
+        <v>773.4</v>
       </c>
       <c r="I3" t="n">
-        <v>3558.5</v>
+        <v>1208.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3889.5</v>
+        <v>1438.7</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0823</v>
+        <v>0.2924</v>
       </c>
     </row>
     <row r="4">
@@ -3604,32 +3616,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4742.9</v>
+        <v>2949.6</v>
       </c>
       <c r="E4" t="n">
-        <v>109.1971922</v>
+        <v>109.193284</v>
       </c>
       <c r="F4" t="n">
-        <v>23.0888466</v>
+        <v>23.0528737</v>
       </c>
       <c r="G4" t="n">
-        <v>746.8</v>
+        <v>822.7</v>
       </c>
       <c r="H4" t="n">
-        <v>5686.9</v>
+        <v>3750.3</v>
       </c>
       <c r="I4" t="n">
-        <v>11472.1</v>
+        <v>9675.700000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>12206.1</v>
+        <v>10266.5</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2528</v>
+        <v>2.2094</v>
       </c>
     </row>
     <row r="5">
@@ -3645,32 +3657,73 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7918.5</v>
+        <v>5292.9</v>
       </c>
       <c r="E5" t="n">
+        <v>109.2284578</v>
+      </c>
+      <c r="F5" t="n">
+        <v>23.0636656</v>
+      </c>
+      <c r="G5" t="n">
+        <v>320.8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5960.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6679.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7137.2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5244</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>R-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10147.1</v>
+      </c>
+      <c r="E6" t="n">
         <v>109.212825</v>
       </c>
-      <c r="F5" t="n">
-        <v>23.0204982</v>
-      </c>
-      <c r="G5" t="n">
-        <v>591.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8333.700000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>9670.700000000001</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9875.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.5527</v>
+      <c r="F6" t="n">
+        <v>23.081652</v>
+      </c>
+      <c r="G6" t="n">
+        <v>577.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11025.4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11756.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12424.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.6674</v>
       </c>
     </row>
   </sheetData>
@@ -3688,32 +3741,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>运输架次编号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>通信阶段</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>开始时刻（s）</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>结束时刻（s）</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>保障方式</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>中继架次编号</t>
         </is>
@@ -3734,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3755,10 +3808,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="D3" t="n">
-        <v>1165.7</v>
+        <v>1170.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3767,7 +3820,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>R-002</t>
+          <t>R-001</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3836,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1165.7</v>
+        <v>1170.7</v>
       </c>
       <c r="D4" t="n">
         <v>1551.7</v>
@@ -3834,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1146.3</v>
+        <v>1141.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3855,10 +3908,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1146.3</v>
+        <v>1141.3</v>
       </c>
       <c r="D7" t="n">
-        <v>2011.2</v>
+        <v>2016.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3883,7 +3936,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2011.2</v>
+        <v>2016.2</v>
       </c>
       <c r="D8" t="n">
         <v>2367.3</v>
@@ -3934,7 +3987,7 @@
         <v>7552.4</v>
       </c>
       <c r="D10" t="n">
-        <v>8446.6</v>
+        <v>8441.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -3955,10 +4008,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8446.6</v>
+        <v>8441.6</v>
       </c>
       <c r="D11" t="n">
-        <v>9670.700000000001</v>
+        <v>9675.700000000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3967,7 +4020,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>R-004</t>
+          <t>R-003</t>
         </is>
       </c>
     </row>
@@ -3983,7 +4036,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9670.700000000001</v>
+        <v>9675.700000000001</v>
       </c>
       <c r="D12" t="n">
         <v>10524.6</v>
@@ -4010,7 +4063,7 @@
         <v>3475.5</v>
       </c>
       <c r="D13" t="n">
-        <v>4277.4</v>
+        <v>4272.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4031,10 +4084,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4277.4</v>
+        <v>4272.4</v>
       </c>
       <c r="D14" t="n">
-        <v>4857.6</v>
+        <v>4862.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4043,7 +4096,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>R-001</t>
+          <t>R-003</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4112,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4857.6</v>
+        <v>4862.6</v>
       </c>
       <c r="D15" t="n">
         <v>5300.2</v>
@@ -4083,10 +4136,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4053.4</v>
+        <v>4332.9</v>
       </c>
       <c r="D16" t="n">
-        <v>5196.8</v>
+        <v>5471.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -4107,10 +4160,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5196.8</v>
+        <v>5471.3</v>
       </c>
       <c r="D17" t="n">
-        <v>5674.4</v>
+        <v>5958.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -4119,7 +4172,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R-001</t>
+          <t>R-003</t>
         </is>
       </c>
     </row>
@@ -4135,10 +4188,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5674.4</v>
+        <v>5958.9</v>
       </c>
       <c r="D18" t="n">
-        <v>5686.9</v>
+        <v>5961.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4159,10 +4212,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5686.9</v>
+        <v>5961.4</v>
       </c>
       <c r="D19" t="n">
-        <v>6395.2</v>
+        <v>6679.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4171,7 +4224,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>R-003</t>
+          <t>R-004</t>
         </is>
       </c>
     </row>
@@ -4187,10 +4240,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6395.2</v>
+        <v>6679.7</v>
       </c>
       <c r="D20" t="n">
-        <v>6932</v>
+        <v>7211.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4214,7 +4267,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>779.4</v>
+        <v>774.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4235,10 +4288,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>779.4</v>
+        <v>774.4</v>
       </c>
       <c r="D22" t="n">
-        <v>1203.3</v>
+        <v>1208.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4247,7 +4300,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R-001</t>
+          <t>R-002</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4316,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1203.3</v>
+        <v>1208.3</v>
       </c>
       <c r="D23" t="n">
         <v>1619.8</v>
@@ -4287,10 +4340,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6932</v>
+        <v>7211.5</v>
       </c>
       <c r="D24" t="n">
-        <v>7820.2</v>
+        <v>8094.7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4311,10 +4364,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7820.2</v>
+        <v>8094.7</v>
       </c>
       <c r="D25" t="n">
-        <v>8321.799999999999</v>
+        <v>8606.299999999999</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4339,10 +4392,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8321.799999999999</v>
+        <v>8606.299999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>8333.700000000001</v>
+        <v>8608.200000000001</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4363,10 +4416,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8333.700000000001</v>
+        <v>8608.200000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>8999.299999999999</v>
+        <v>9283.799999999999</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4375,7 +4428,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R-004</t>
+          <t>R-003</t>
         </is>
       </c>
     </row>
@@ -4391,10 +4444,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8999.299999999999</v>
+        <v>9283.799999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>9348.4</v>
+        <v>9627.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -4418,7 +4471,7 @@
         <v>1492</v>
       </c>
       <c r="D29" t="n">
-        <v>2344</v>
+        <v>2339</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -4439,10 +4492,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2344</v>
+        <v>2339</v>
       </c>
       <c r="D30" t="n">
-        <v>3558.5</v>
+        <v>3563.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -4451,7 +4504,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>R-002</t>
+          <t>R-001</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4520,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3558.5</v>
+        <v>3563.5</v>
       </c>
       <c r="D31" t="n">
         <v>4053.4</v>
@@ -4494,7 +4547,7 @@
         <v>2367.3</v>
       </c>
       <c r="D32" t="n">
-        <v>3645.5</v>
+        <v>3640.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -4515,10 +4568,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3645.5</v>
+        <v>3640.5</v>
       </c>
       <c r="D33" t="n">
-        <v>4510.4</v>
+        <v>4515.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -4543,7 +4596,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4510.4</v>
+        <v>4515.4</v>
       </c>
       <c r="D34" t="n">
         <v>4866.6</v>
@@ -4570,7 +4623,7 @@
         <v>3007</v>
       </c>
       <c r="D35" t="n">
-        <v>3756.3</v>
+        <v>3751.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -4591,10 +4644,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3756.3</v>
+        <v>3751.3</v>
       </c>
       <c r="D36" t="n">
-        <v>4734</v>
+        <v>4739</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -4603,7 +4656,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>R-001</t>
+          <t>R-003</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4672,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4734</v>
+        <v>4739</v>
       </c>
       <c r="D37" t="n">
         <v>5168.3</v>
@@ -4646,7 +4699,7 @@
         <v>1551.7</v>
       </c>
       <c r="D38" t="n">
-        <v>2301.9</v>
+        <v>2296.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -4667,10 +4720,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2301.9</v>
+        <v>2296.9</v>
       </c>
       <c r="D39" t="n">
-        <v>3098</v>
+        <v>3103</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -4679,7 +4732,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>R-002</t>
+          <t>R-001</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4748,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3098</v>
+        <v>3103</v>
       </c>
       <c r="D40" t="n">
         <v>3475.5</v>
@@ -4746,7 +4799,7 @@
         <v>5168.3</v>
       </c>
       <c r="D42" t="n">
-        <v>5965.2</v>
+        <v>5960.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -4767,10 +4820,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5965.2</v>
+        <v>5960.2</v>
       </c>
       <c r="D43" t="n">
-        <v>6801.9</v>
+        <v>6806.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -4779,7 +4832,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>R-001</t>
+          <t>R-003</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4848,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6801.9</v>
+        <v>6806.9</v>
       </c>
       <c r="D44" t="n">
         <v>7236.2</v>
@@ -4819,10 +4872,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9485.6</v>
+        <v>9765.1</v>
       </c>
       <c r="D45" t="n">
-        <v>10751.9</v>
+        <v>11026.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -4843,10 +4896,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>10751.9</v>
+        <v>11026.4</v>
       </c>
       <c r="D46" t="n">
-        <v>11472.1</v>
+        <v>11756.6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -4855,7 +4908,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>R-003</t>
+          <t>R-005</t>
         </is>
       </c>
     </row>
@@ -4871,10 +4924,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>11472.1</v>
+        <v>11756.6</v>
       </c>
       <c r="D47" t="n">
-        <v>12008.9</v>
+        <v>12288.3</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -4898,7 +4951,7 @@
         <v>4866.6</v>
       </c>
       <c r="D48" t="n">
-        <v>6287.8</v>
+        <v>6282.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -4919,10 +4972,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6287.8</v>
+        <v>6282.8</v>
       </c>
       <c r="D49" t="n">
-        <v>7137</v>
+        <v>7142</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -4931,7 +4984,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>R-001</t>
+          <t>R-003</t>
         </is>
       </c>
     </row>
@@ -4947,7 +5000,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7137</v>
+        <v>7142</v>
       </c>
       <c r="D50" t="n">
         <v>7552.4</v>
@@ -4974,57 +5027,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>K（2或3）</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>任务组编号</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>服务区列表</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>A型运输无人机数</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>B型运输无人机数</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>C型运输无人机数</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>A型电池组数</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>B型电池组数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>C型电池组数</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>中继无人机数</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>中继能源组件数</t>
         </is>
@@ -5119,14 +5172,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S001;S002;S004;S005;S009;S015</t>
+          <t>S001;S002;S004;S005;S009;S013;S014</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -5135,10 +5188,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -5158,7 +5211,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S003;S006;S007;S008;S010;S011;S012;S013;S014</t>
+          <t>S003;S006;S007;S008;S010;S011;S012;S015</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -5353,7 +5406,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S003;S006;S007</t>
+          <t>S003;S006;S007;S010</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -5375,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
@@ -5392,7 +5445,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>S008;S010;S011;S012;S013;S014;S015</t>
+          <t>S008;S011;S012;S013;S014;S015</t>
         </is>
       </c>
       <c r="D11" t="n">
